--- a/Team-Data/2014-15/3-12-2014-15.xlsx
+++ b/Team-Data/2014-15/3-12-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>6.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -751,13 +818,13 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
         <v>13</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
         <v>3</v>
@@ -775,7 +842,7 @@
         <v>14</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
         <v>4</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -921,19 +988,19 @@
         <v>-1.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF3" t="n">
         <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI3" t="n">
         <v>5</v>
@@ -966,7 +1033,7 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -981,7 +1048,7 @@
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
@@ -1151,7 +1218,7 @@
         <v>19</v>
       </c>
       <c r="AT4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU4" t="n">
         <v>27</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
         <v>19</v>
@@ -1321,7 +1388,7 @@
         <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
         <v>23</v>
@@ -1333,10 +1400,10 @@
         <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1345,7 +1412,7 @@
         <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
         <v>21</v>
@@ -1354,7 +1421,7 @@
         <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
         <v>27</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
@@ -1485,7 +1552,7 @@
         <v>22</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK6" t="n">
         <v>21</v>
@@ -1527,7 +1594,7 @@
         <v>29</v>
       </c>
       <c r="AX6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -1571,61 +1638,61 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" t="n">
         <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>0.627</v>
+        <v>0.621</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J7" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L7" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="M7" t="n">
         <v>26.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.359</v>
+        <v>0.356</v>
       </c>
       <c r="O7" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P7" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.758</v>
+        <v>0.756</v>
       </c>
       <c r="R7" t="n">
         <v>11.3</v>
       </c>
       <c r="S7" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U7" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V7" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W7" t="n">
         <v>7.4</v>
@@ -1634,16 +1701,16 @@
         <v>4.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>103.3</v>
+        <v>102.9</v>
       </c>
       <c r="AC7" t="n">
         <v>4.5</v>
@@ -1652,22 +1719,22 @@
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG7" t="n">
         <v>8</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AI7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK7" t="n">
         <v>10</v>
@@ -1682,10 +1749,10 @@
         <v>8</v>
       </c>
       <c r="AO7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
         <v>17</v>
@@ -1694,7 +1761,7 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT7" t="n">
         <v>17</v>
@@ -1718,10 +1785,10 @@
         <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
         <v>5</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E8" t="n">
         <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>0.631</v>
+        <v>0.621</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,7 +1838,7 @@
         <v>39.3</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
         <v>0.459</v>
@@ -1780,40 +1847,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="N8" t="n">
         <v>0.349</v>
       </c>
       <c r="O8" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P8" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R8" t="n">
         <v>10.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V8" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y8" t="n">
         <v>3.8</v>
@@ -1828,22 +1895,22 @@
         <v>104.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF8" t="n">
         <v>8</v>
       </c>
-      <c r="AF8" t="n">
-        <v>7</v>
-      </c>
       <c r="AG8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1852,7 +1919,7 @@
         <v>9</v>
       </c>
       <c r="AK8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL8" t="n">
         <v>7</v>
@@ -1864,22 +1931,22 @@
         <v>13</v>
       </c>
       <c r="AO8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ8" t="n">
         <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1891,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1906,7 +1973,7 @@
         <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2058,7 +2125,7 @@
         <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
@@ -2073,7 +2140,7 @@
         <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,19 +2274,19 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>20</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK10" t="n">
         <v>29</v>
       </c>
       <c r="AL10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM10" t="n">
         <v>11</v>
@@ -2231,7 +2298,7 @@
         <v>23</v>
       </c>
       <c r="AP10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
@@ -2240,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
         <v>4</v>
@@ -2264,7 +2331,7 @@
         <v>9</v>
       </c>
       <c r="BA10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>10.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2389,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
@@ -2410,19 +2477,19 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
         <v>25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -2484,13 +2551,13 @@
         <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>0.656</v>
+        <v>0.672</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,43 +2566,43 @@
         <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
       </c>
       <c r="L12" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="M12" t="n">
         <v>33.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.346</v>
       </c>
       <c r="O12" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="R12" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="U12" t="n">
         <v>22</v>
       </c>
       <c r="V12" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="W12" t="n">
         <v>9.6</v>
@@ -2544,22 +2611,22 @@
         <v>4.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>103</v>
+        <v>103.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2571,7 +2638,7 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
         <v>19</v>
@@ -2595,7 +2662,7 @@
         <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
@@ -2604,16 +2671,16 @@
         <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW12" t="n">
         <v>2</v>
@@ -2622,19 +2689,19 @@
         <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" t="n">
         <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>0.469</v>
+        <v>0.46</v>
       </c>
       <c r="H13" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J13" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L13" t="n">
         <v>7.1</v>
@@ -2693,22 +2760,22 @@
         <v>20.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.341</v>
+        <v>0.339</v>
       </c>
       <c r="O13" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P13" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q13" t="n">
         <v>0.764</v>
       </c>
       <c r="R13" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S13" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="T13" t="n">
         <v>45.1</v>
@@ -2717,31 +2784,31 @@
         <v>21.5</v>
       </c>
       <c r="V13" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W13" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X13" t="n">
         <v>4.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB13" t="n">
-        <v>96.7</v>
+        <v>96.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AE13" t="n">
         <v>17</v>
@@ -2753,13 +2820,13 @@
         <v>17</v>
       </c>
       <c r="AH13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK13" t="n">
         <v>23</v>
@@ -2768,13 +2835,13 @@
         <v>18</v>
       </c>
       <c r="AM13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN13" t="n">
         <v>20</v>
       </c>
       <c r="AO13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP13" t="n">
         <v>23</v>
@@ -2783,7 +2850,7 @@
         <v>13</v>
       </c>
       <c r="AR13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
@@ -2801,7 +2868,7 @@
         <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY13" t="n">
         <v>17</v>
@@ -2810,13 +2877,13 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
         <v>23</v>
       </c>
       <c r="BC13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>6.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2935,7 +3002,7 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2989,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -3042,40 +3109,40 @@
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J15" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L15" t="n">
         <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N15" t="n">
         <v>0.342</v>
       </c>
       <c r="O15" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="P15" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="R15" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T15" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="U15" t="n">
         <v>20.9</v>
@@ -3090,22 +3157,22 @@
         <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,10 +3187,10 @@
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
@@ -3144,16 +3211,16 @@
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT15" t="n">
         <v>11</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>10</v>
       </c>
       <c r="AU15" t="n">
         <v>20</v>
@@ -3168,16 +3235,16 @@
         <v>20</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -3209,61 +3276,61 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" t="n">
         <v>45</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
       </c>
       <c r="I16" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J16" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M16" t="n">
         <v>15.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.331</v>
+        <v>0.334</v>
       </c>
       <c r="O16" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P16" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="R16" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S16" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T16" t="n">
         <v>42.7</v>
       </c>
       <c r="U16" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V16" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="W16" t="n">
         <v>8.699999999999999</v>
@@ -3275,19 +3342,19 @@
         <v>5.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3302,13 +3369,13 @@
         <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,7 +3384,7 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>7</v>
@@ -3338,7 +3405,7 @@
         <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV16" t="n">
         <v>6</v>
@@ -3353,16 +3420,16 @@
         <v>23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA16" t="n">
         <v>14</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>-2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF17" t="n">
         <v>18</v>
@@ -3481,7 +3548,7 @@
         <v>18</v>
       </c>
       <c r="AH17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
         <v>29</v>
@@ -3493,7 +3560,7 @@
         <v>12</v>
       </c>
       <c r="AL17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM17" t="n">
         <v>19</v>
@@ -3505,10 +3572,10 @@
         <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3538,7 +3605,7 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E18" t="n">
         <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>0.523</v>
+        <v>0.531</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3591,43 +3658,43 @@
         <v>37.4</v>
       </c>
       <c r="J18" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K18" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L18" t="n">
         <v>6.9</v>
       </c>
       <c r="M18" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O18" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R18" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S18" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T18" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U18" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="V18" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="W18" t="n">
         <v>9.6</v>
@@ -3639,19 +3706,19 @@
         <v>4.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
@@ -3663,19 +3730,19 @@
         <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI18" t="n">
         <v>16</v>
       </c>
       <c r="AJ18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK18" t="n">
         <v>5</v>
       </c>
       <c r="AL18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="n">
         <v>25</v>
@@ -3684,7 +3751,7 @@
         <v>3</v>
       </c>
       <c r="AO18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP18" t="n">
         <v>26</v>
@@ -3705,7 +3772,7 @@
         <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW18" t="n">
         <v>3</v>
@@ -3714,7 +3781,7 @@
         <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ18" t="n">
         <v>25</v>
@@ -3726,7 +3793,7 @@
         <v>21</v>
       </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3845,7 +3912,7 @@
         <v>28</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
         <v>23</v>
@@ -3884,7 +3951,7 @@
         <v>24</v>
       </c>
       <c r="AU19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV19" t="n">
         <v>22</v>
@@ -3899,10 +3966,10 @@
         <v>27</v>
       </c>
       <c r="AZ19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20" t="n">
         <v>29</v>
       </c>
       <c r="G20" t="n">
-        <v>0.547</v>
+        <v>0.554</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J20" t="n">
-        <v>82.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
@@ -3967,37 +4034,37 @@
         <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="O20" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P20" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.772</v>
+        <v>0.766</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
         <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="U20" t="n">
         <v>21.8</v>
       </c>
       <c r="V20" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W20" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,19 +4073,19 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
         <v>99.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
@@ -4027,40 +4094,40 @@
         <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM20" t="n">
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR20" t="n">
         <v>8</v>
       </c>
-      <c r="AR20" t="n">
-        <v>10</v>
-      </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
         <v>16</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21" t="n">
         <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>0.203</v>
+        <v>0.19</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
@@ -4137,10 +4204,10 @@
         <v>35.4</v>
       </c>
       <c r="J21" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L21" t="n">
         <v>6.9</v>
@@ -4149,55 +4216,55 @@
         <v>19.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O21" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="P21" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="Q21" t="n">
         <v>0.769</v>
       </c>
       <c r="R21" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S21" t="n">
         <v>29.6</v>
       </c>
       <c r="T21" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U21" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V21" t="n">
         <v>14.3</v>
       </c>
       <c r="W21" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y21" t="n">
         <v>4.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4215,19 +4282,19 @@
         <v>28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK21" t="n">
         <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
         <v>17</v>
@@ -4263,7 +4330,7 @@
         <v>7</v>
       </c>
       <c r="AZ21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -4379,25 +4446,25 @@
         <v>2.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF22" t="n">
         <v>13</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK22" t="n">
         <v>18</v>
@@ -4412,7 +4479,7 @@
         <v>25</v>
       </c>
       <c r="AO22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP22" t="n">
         <v>11</v>
@@ -4445,7 +4512,7 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
         <v>18</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -4483,55 +4550,55 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E23" t="n">
         <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G23" t="n">
-        <v>0.323</v>
+        <v>0.318</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J23" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
         <v>0.355</v>
       </c>
       <c r="O23" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="P23" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.731</v>
+        <v>0.732</v>
       </c>
       <c r="R23" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>40.9</v>
+        <v>41.1</v>
       </c>
       <c r="U23" t="n">
         <v>20.4</v>
@@ -4540,13 +4607,13 @@
         <v>14.9</v>
       </c>
       <c r="W23" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>21.1</v>
@@ -4555,13 +4622,13 @@
         <v>18.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.6</v>
+        <v>-5.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4585,7 +4652,7 @@
         <v>13</v>
       </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
@@ -4600,13 +4667,13 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR23" t="n">
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
         <v>27</v>
@@ -4618,16 +4685,16 @@
         <v>23</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>20</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>19</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4761,7 +4828,7 @@
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
@@ -4779,13 +4846,13 @@
         <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4812,7 +4879,7 @@
         <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>0.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4958,10 +5025,10 @@
         <v>12</v>
       </c>
       <c r="AO25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ25" t="n">
         <v>7</v>
@@ -4985,7 +5052,7 @@
         <v>6</v>
       </c>
       <c r="AX25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
@@ -4994,7 +5061,7 @@
         <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB25" t="n">
         <v>3</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -5110,10 +5177,10 @@
         <v>30</v>
       </c>
       <c r="AE26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF26" t="n">
         <v>4</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>3</v>
       </c>
       <c r="AG26" t="n">
         <v>4</v>
@@ -5125,7 +5192,7 @@
         <v>10</v>
       </c>
       <c r="AJ26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK26" t="n">
         <v>19</v>
@@ -5137,10 +5204,10 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP26" t="n">
         <v>27</v>
@@ -5158,7 +5225,7 @@
         <v>2</v>
       </c>
       <c r="AU26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV26" t="n">
         <v>9</v>
@@ -5176,7 +5243,7 @@
         <v>5</v>
       </c>
       <c r="BA26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB26" t="n">
         <v>9</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -5396,97 +5463,97 @@
         <v>63</v>
       </c>
       <c r="E28" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G28" t="n">
-        <v>0.619</v>
+        <v>0.635</v>
       </c>
       <c r="H28" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.362</v>
+        <v>0.365</v>
       </c>
       <c r="O28" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P28" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.77</v>
+        <v>0.772</v>
       </c>
       <c r="R28" t="n">
         <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U28" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="V28" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W28" t="n">
         <v>7.8</v>
       </c>
       <c r="X28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
         <v>4.7</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA28" t="n">
         <v>20</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.9</v>
+        <v>101.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG28" t="n">
         <v>7</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>9</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
         <v>14</v>
@@ -5495,28 +5562,28 @@
         <v>9</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR28" t="n">
         <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>15</v>
@@ -5531,13 +5598,13 @@
         <v>13</v>
       </c>
       <c r="AX28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA28" t="n">
         <v>19</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5665,7 +5732,7 @@
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI29" t="n">
         <v>9</v>
@@ -5683,13 +5750,13 @@
         <v>9</v>
       </c>
       <c r="AN29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO29" t="n">
         <v>4</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
         <v>3</v>
@@ -5710,10 +5777,10 @@
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
@@ -5728,7 +5795,7 @@
         <v>4</v>
       </c>
       <c r="BC29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -5757,55 +5824,55 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F30" t="n">
         <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>0.438</v>
+        <v>0.429</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J30" t="n">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="K30" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L30" t="n">
         <v>7.2</v>
       </c>
       <c r="M30" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N30" t="n">
         <v>0.343</v>
       </c>
       <c r="O30" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P30" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.73</v>
+        <v>0.732</v>
       </c>
       <c r="R30" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="S30" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T30" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
       <c r="U30" t="n">
         <v>20.1</v>
@@ -5817,7 +5884,7 @@
         <v>7.3</v>
       </c>
       <c r="X30" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y30" t="n">
         <v>4.8</v>
@@ -5829,16 +5896,16 @@
         <v>19.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>95.3</v>
+        <v>95</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AE30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF30" t="n">
         <v>20</v>
@@ -5862,28 +5929,28 @@
         <v>17</v>
       </c>
       <c r="AM30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN30" t="n">
         <v>17</v>
       </c>
       <c r="AO30" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AP30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR30" t="n">
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AT30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU30" t="n">
         <v>28</v>
@@ -5892,19 +5959,19 @@
         <v>26</v>
       </c>
       <c r="AW30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
         <v>15</v>
       </c>
       <c r="AZ30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F31" t="n">
         <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>0.569</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
@@ -5957,10 +6024,10 @@
         <v>38.4</v>
       </c>
       <c r="J31" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L31" t="n">
         <v>5.9</v>
@@ -5969,16 +6036,16 @@
         <v>16.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O31" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="P31" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R31" t="n">
         <v>10.6</v>
@@ -5987,7 +6054,7 @@
         <v>33.6</v>
       </c>
       <c r="T31" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="U31" t="n">
         <v>24.1</v>
@@ -6008,16 +6075,16 @@
         <v>21.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6029,10 +6096,10 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AI31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ31" t="n">
         <v>20</v>
@@ -6059,10 +6126,10 @@
         <v>19</v>
       </c>
       <c r="AR31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
         <v>9</v>
@@ -6083,16 +6150,16 @@
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-12-2014-15</t>
+          <t>2015-03-12</t>
         </is>
       </c>
     </row>
